--- a/data/trans_orig/P36A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36A-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la cantidad de agua que consumen al día en 2012</t>
+          <t>Población según la cantidad de agua que consumen al día en 2012 (tasa de respuesta: 98,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106375</t>
+          <t>106481</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>147635</t>
+          <t>148171</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>79666</t>
+          <t>80866</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>117030</t>
+          <t>119674</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>197745</t>
+          <t>195746</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>257020</t>
+          <t>256120</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>163295</t>
+          <t>161963</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>215708</t>
+          <t>215717</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>201114</t>
+          <t>203530</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>256366</t>
+          <t>259583</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>377234</t>
+          <t>378371</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>451857</t>
+          <t>454926</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>267961</t>
+          <t>266772</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>327156</t>
+          <t>327848</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>410999</t>
+          <t>409589</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>477599</t>
+          <t>480601</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>693872</t>
+          <t>697011</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>786761</t>
+          <t>788285</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>240494</t>
+          <t>239589</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>297617</t>
+          <t>298463</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>396666</t>
+          <t>395533</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>463886</t>
+          <t>464911</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>649723</t>
+          <t>649260</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>744145</t>
+          <t>739807</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,38%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68171</t>
+          <t>67181</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102016</t>
+          <t>103458</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>103406</t>
+          <t>102633</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>144498</t>
+          <t>147151</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>180902</t>
+          <t>180218</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>241012</t>
+          <t>235013</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -1297,97 +1297,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2061</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2060</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>2061</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296266</t>
+          <t>297839</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>365571</t>
+          <t>366224</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>184105</t>
+          <t>183654</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>238798</t>
+          <t>240063</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>496281</t>
+          <t>501197</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>584298</t>
+          <t>588007</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>498583</t>
+          <t>499371</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>577314</t>
+          <t>576765</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>399049</t>
+          <t>403564</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>478430</t>
+          <t>480696</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>920305</t>
+          <t>917801</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1031017</t>
+          <t>1029521</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>612305</t>
+          <t>615966</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>697153</t>
+          <t>701712</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>489628</t>
+          <t>491228</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>569780</t>
+          <t>569528</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1125366</t>
+          <t>1130237</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1241442</t>
+          <t>1237879</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,76%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>303131</t>
+          <t>306784</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>375257</t>
+          <t>371119</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>379976</t>
+          <t>378948</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>452002</t>
+          <t>449797</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>706088</t>
+          <t>705342</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>803673</t>
+          <t>805976</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60627</t>
+          <t>60201</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>95782</t>
+          <t>96714</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>112879</t>
+          <t>114686</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>159939</t>
+          <t>160637</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>186426</t>
+          <t>182945</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>248287</t>
+          <t>243579</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -2092,97 +2092,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2064</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64457</t>
+          <t>62774</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100182</t>
+          <t>99663</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>47568</t>
+          <t>48222</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>77402</t>
+          <t>76736</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>121088</t>
+          <t>121407</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>166446</t>
+          <t>169588</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>118291</t>
+          <t>119261</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>161570</t>
+          <t>160382</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>104675</t>
+          <t>104525</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>143226</t>
+          <t>145879</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>234405</t>
+          <t>232118</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>288602</t>
+          <t>290855</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,29%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>136576</t>
+          <t>137661</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>181652</t>
+          <t>180687</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>125279</t>
+          <t>125699</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>166640</t>
+          <t>167711</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>273675</t>
+          <t>275379</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>335111</t>
+          <t>333303</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,86%</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>62923</t>
+          <t>63384</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>100743</t>
+          <t>100035</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>76511</t>
+          <t>75036</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>112319</t>
+          <t>113506</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>150499</t>
+          <t>148383</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>201923</t>
+          <t>199558</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9593</t>
+          <t>9292</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25415</t>
+          <t>25855</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20036</t>
+          <t>20755</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42950</t>
+          <t>43642</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35653</t>
+          <t>33750</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62375</t>
+          <t>61422</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -2887,97 +2887,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2109</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2130</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>2122</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>494767</t>
+          <t>490205</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>581296</t>
+          <t>580476</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>334770</t>
+          <t>337337</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>409493</t>
+          <t>410985</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>847472</t>
+          <t>849138</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>972834</t>
+          <t>967855</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>809891</t>
+          <t>813749</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>919592</t>
+          <t>919064</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>742096</t>
+          <t>741876</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>844346</t>
+          <t>844043</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1581892</t>
+          <t>1582711</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1731777</t>
+          <t>1733062</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1049604</t>
+          <t>1058368</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1163996</t>
+          <t>1162001</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1058058</t>
+          <t>1064748</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1178512</t>
+          <t>1174349</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2146962</t>
+          <t>2141634</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2305837</t>
+          <t>2299710</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,42%</t>
         </is>
       </c>
     </row>
@@ -3456,12 +3456,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>642299</t>
+          <t>642860</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>737329</t>
+          <t>734932</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>885759</t>
+          <t>883378</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>990292</t>
+          <t>991620</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1554796</t>
+          <t>1553576</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1699919</t>
+          <t>1695728</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>150421</t>
+          <t>153493</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>203166</t>
+          <t>204458</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>257160</t>
+          <t>260517</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>325439</t>
+          <t>329993</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>427537</t>
+          <t>428052</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>510196</t>
+          <t>512507</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -3682,97 +3682,97 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>2052</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>2063</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3948,7 +3948,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la cantidad de agua que consumen al día en 2016</t>
+          <t>Población según la cantidad de agua que consumen al día en 2016 (tasa de respuesta: 98,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90979</t>
+          <t>91310</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>130474</t>
+          <t>129954</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>75194</t>
+          <t>74998</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113053</t>
+          <t>111707</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>176618</t>
+          <t>176010</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>230497</t>
+          <t>230314</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -4256,12 +4256,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>142872</t>
+          <t>145435</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>190187</t>
+          <t>191662</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>206185</t>
+          <t>204080</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259622</t>
+          <t>258866</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>360628</t>
+          <t>364557</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>430916</t>
+          <t>436132</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -4369,12 +4369,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>199998</t>
+          <t>201970</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>248800</t>
+          <t>251538</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>305506</t>
+          <t>304809</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>366421</t>
+          <t>364016</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>520386</t>
+          <t>520981</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>596282</t>
+          <t>595978</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,77%</t>
         </is>
       </c>
     </row>
@@ -4482,12 +4482,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>153144</t>
+          <t>151417</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>198804</t>
+          <t>198202</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>224092</t>
+          <t>223800</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>278551</t>
+          <t>280864</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4532,12 +4532,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>390088</t>
+          <t>394869</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>461287</t>
+          <t>467851</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4567,12 +4567,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -4595,12 +4595,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45239</t>
+          <t>45335</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72188</t>
+          <t>73533</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4610,12 +4610,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53236</t>
+          <t>55105</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>88213</t>
+          <t>89056</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>107618</t>
+          <t>107745</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>151975</t>
+          <t>151773</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -4708,97 +4708,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1898</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2140</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311101</t>
+          <t>308749</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>378494</t>
+          <t>380179</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>217015</t>
+          <t>217963</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>275775</t>
+          <t>276884</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>547175</t>
+          <t>545614</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>637349</t>
+          <t>636224</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>527073</t>
+          <t>527681</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>614355</t>
+          <t>608800</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>515137</t>
+          <t>514616</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>595487</t>
+          <t>595578</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1063184</t>
+          <t>1064877</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1178518</t>
+          <t>1179216</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -5164,12 +5164,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>701686</t>
+          <t>699094</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>785753</t>
+          <t>784974</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>685516</t>
+          <t>690279</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>774637</t>
+          <t>775165</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5214,12 +5214,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1415997</t>
+          <t>1409514</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1534733</t>
+          <t>1533529</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,51%</t>
         </is>
       </c>
     </row>
@@ -5277,12 +5277,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>279989</t>
+          <t>281622</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>347122</t>
+          <t>347360</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5292,12 +5292,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>302245</t>
+          <t>300226</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>371302</t>
+          <t>367878</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>595730</t>
+          <t>596106</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>696409</t>
+          <t>692415</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -5390,12 +5390,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48692</t>
+          <t>50196</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>79218</t>
+          <t>80503</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5405,12 +5405,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>74459</t>
+          <t>70733</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>114717</t>
+          <t>110790</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>128310</t>
+          <t>130109</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>182398</t>
+          <t>180562</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -5503,97 +5503,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2040</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5733,12 +5733,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>87825</t>
+          <t>89712</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>127477</t>
+          <t>129258</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5748,12 +5748,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65954</t>
+          <t>64321</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>98268</t>
+          <t>99200</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>165053</t>
+          <t>165104</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>215246</t>
+          <t>214203</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -5846,12 +5846,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>154214</t>
+          <t>153649</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>201223</t>
+          <t>201423</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>156259</t>
+          <t>157880</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>200145</t>
+          <t>198994</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>324113</t>
+          <t>322818</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>388006</t>
+          <t>383649</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,44%</t>
         </is>
       </c>
     </row>
@@ -5959,12 +5959,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>152661</t>
+          <t>151400</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>195251</t>
+          <t>197963</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5974,12 +5974,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>162136</t>
+          <t>162292</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>323326</t>
+          <t>322717</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>387795</t>
+          <t>385482</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -6072,12 +6072,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>59983</t>
+          <t>59797</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>92080</t>
+          <t>93143</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>68122</t>
+          <t>69978</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>102630</t>
+          <t>105129</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6142,12 +6142,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>138675</t>
+          <t>138462</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>188858</t>
+          <t>190587</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,6%</t>
         </is>
       </c>
     </row>
@@ -6185,12 +6185,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18678</t>
+          <t>18195</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6220,12 +6220,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>7606</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22258</t>
+          <t>21782</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15840</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34759</t>
+          <t>35538</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -6298,97 +6298,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2094</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6528,12 +6528,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>515027</t>
+          <t>521092</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>603101</t>
+          <t>603113</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>378244</t>
+          <t>380884</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>458728</t>
+          <t>459284</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6598,12 +6598,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>924762</t>
+          <t>923295</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1045750</t>
+          <t>1042759</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -6641,12 +6641,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>860472</t>
+          <t>862086</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>962298</t>
+          <t>964137</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6676,12 +6676,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>909175</t>
+          <t>910218</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1016472</t>
+          <t>1014763</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6711,12 +6711,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1791331</t>
+          <t>1800936</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1943078</t>
+          <t>1953823</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,82%</t>
         </is>
       </c>
     </row>
@@ -6754,12 +6754,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1083219</t>
+          <t>1082264</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1193356</t>
+          <t>1193634</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -6789,12 +6789,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1188687</t>
+          <t>1188543</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1312223</t>
+          <t>1297369</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6824,12 +6824,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2302404</t>
+          <t>2300888</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2461647</t>
+          <t>2467879</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,41%</t>
         </is>
       </c>
     </row>
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>520156</t>
+          <t>520530</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>608278</t>
+          <t>608254</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>624958</t>
+          <t>627604</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>714806</t>
+          <t>719064</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1168503</t>
+          <t>1172141</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1302294</t>
+          <t>1306750</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -6980,12 +6980,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>109983</t>
+          <t>109060</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>157221</t>
+          <t>155533</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6995,12 +6995,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>150960</t>
+          <t>148251</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>205315</t>
+          <t>202345</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>271164</t>
+          <t>272383</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>340850</t>
+          <t>344650</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -7093,97 +7093,97 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la cantidad de agua que consumen al día en 2023</t>
+          <t>Población según la cantidad de agua que consumen al día en 2023 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99100</t>
+          <t>99001</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>135718</t>
+          <t>134808</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>105541</t>
+          <t>105737</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>136356</t>
+          <t>134161</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>214416</t>
+          <t>214440</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>260048</t>
+          <t>260278</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -7667,12 +7667,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132767</t>
+          <t>134091</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>172146</t>
+          <t>172452</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7682,12 +7682,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>232501</t>
+          <t>233322</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>273123</t>
+          <t>272627</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>376513</t>
+          <t>380225</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>431720</t>
+          <t>431746</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7780,12 +7780,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>131427</t>
+          <t>132770</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>171317</t>
+          <t>168873</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7795,12 +7795,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7815,12 +7815,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>213273</t>
+          <t>215434</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>253897</t>
+          <t>254928</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>357631</t>
+          <t>355535</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>410710</t>
+          <t>407779</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -7893,12 +7893,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54478</t>
+          <t>52674</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83704</t>
+          <t>80854</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7928,12 +7928,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92149</t>
+          <t>92536</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>128516</t>
+          <t>128206</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7963,12 +7963,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>156730</t>
+          <t>156357</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>198704</t>
+          <t>201649</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -8006,12 +8006,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11138</t>
+          <t>10855</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25424</t>
+          <t>25401</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8021,12 +8021,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8041,12 +8041,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21097</t>
+          <t>20141</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36222</t>
+          <t>35390</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35228</t>
+          <t>34531</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56374</t>
+          <t>57483</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -8119,12 +8119,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>713</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8434</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8154,12 +8154,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>3073</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12553</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>672134</t>
+          <t>670719</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1336467</t>
+          <t>1309984</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8364,12 +8364,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8384,12 +8384,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>310689</t>
+          <t>293575</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>481699</t>
+          <t>477479</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8419,12 +8419,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1047430</t>
+          <t>1044332</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1854929</t>
+          <t>1835947</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,66%</t>
         </is>
       </c>
     </row>
@@ -8462,12 +8462,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>514890</t>
+          <t>536973</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>857426</t>
+          <t>860913</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>503322</t>
+          <t>534975</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>817791</t>
+          <t>827023</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1198944</t>
+          <t>1163555</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1652119</t>
+          <t>1637271</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,26%</t>
         </is>
       </c>
     </row>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>327415</t>
+          <t>356477</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>575894</t>
+          <t>580682</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8610,12 +8610,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>613497</t>
+          <t>605852</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1217545</t>
+          <t>1208543</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1062256</t>
+          <t>1059273</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1878939</t>
+          <t>1760869</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>39,0%</t>
         </is>
       </c>
     </row>
@@ -8688,12 +8688,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93657</t>
+          <t>97484</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170418</t>
+          <t>173588</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8703,12 +8703,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>168393</t>
+          <t>169637</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>273996</t>
+          <t>277407</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>303197</t>
+          <t>299097</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>430865</t>
+          <t>431869</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -8801,12 +8801,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19227</t>
+          <t>19222</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44423</t>
+          <t>43527</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>40989</t>
+          <t>42038</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>76145</t>
+          <t>76870</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8851,12 +8851,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8871,12 +8871,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>68795</t>
+          <t>67981</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>111108</t>
+          <t>110659</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8886,12 +8886,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -8914,12 +8914,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10327</t>
+          <t>9667</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8929,77 +8929,77 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>4029</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1373</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8994</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>0,06%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4029</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1345</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>9083</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>8145</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>4060</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>15645</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>8145</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>3746</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>15976</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>166927</t>
+          <t>167065</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>220319</t>
+          <t>220410</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9159,12 +9159,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>142930</t>
+          <t>143479</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>183875</t>
+          <t>182405</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>320433</t>
+          <t>323409</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>390052</t>
+          <t>388181</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,74%</t>
         </is>
       </c>
     </row>
@@ -9257,12 +9257,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>218353</t>
+          <t>216179</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>272448</t>
+          <t>268646</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9272,12 +9272,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>207782</t>
+          <t>206129</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>250787</t>
+          <t>248507</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9307,12 +9307,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>437020</t>
+          <t>432362</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>503348</t>
+          <t>502220</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9342,12 +9342,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -9370,12 +9370,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>132491</t>
+          <t>134111</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>186502</t>
+          <t>185744</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9385,12 +9385,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>152197</t>
+          <t>153959</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>192459</t>
+          <t>191560</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9420,12 +9420,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9440,12 +9440,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>302962</t>
+          <t>301195</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>366891</t>
+          <t>366376</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9455,12 +9455,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -9483,12 +9483,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31537</t>
+          <t>31960</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>57884</t>
+          <t>58196</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64077</t>
+          <t>63989</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>92421</t>
+          <t>94186</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9533,12 +9533,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>101301</t>
+          <t>101637</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>141117</t>
+          <t>141154</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14227</t>
+          <t>13719</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10889</t>
+          <t>11557</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27778</t>
+          <t>27734</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9646,12 +9646,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16720</t>
+          <t>17612</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36483</t>
+          <t>38236</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9681,12 +9681,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -9709,12 +9709,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>715</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7316</t>
+          <t>8012</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>696</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6891</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9759,12 +9759,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11048</t>
+          <t>11054</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>973795</t>
+          <t>970730</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1596947</t>
+          <t>1687344</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9974,12 +9974,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>566779</t>
+          <t>560816</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>761077</t>
+          <t>768476</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9989,12 +9989,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1625680</t>
+          <t>1621534</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2414949</t>
+          <t>2494280</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10024,12 +10024,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>35,27%</t>
         </is>
       </c>
     </row>
@@ -10052,12 +10052,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>899085</t>
+          <t>882892</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1250437</t>
+          <t>1259078</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10087,12 +10087,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>979824</t>
+          <t>968947</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1305583</t>
+          <t>1304660</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10102,12 +10102,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2044871</t>
+          <t>2032622</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2511752</t>
+          <t>2527688</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -10165,12 +10165,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>635574</t>
+          <t>632231</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>897289</t>
+          <t>895763</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10200,12 +10200,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1017003</t>
+          <t>1015910</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1699275</t>
+          <t>1696302</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10215,12 +10215,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10235,12 +10235,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1797833</t>
+          <t>1780041</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2601681</t>
+          <t>2516337</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>35,59%</t>
         </is>
       </c>
     </row>
@@ -10278,12 +10278,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>195407</t>
+          <t>197872</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>288071</t>
+          <t>288719</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10293,12 +10293,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10313,12 +10313,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>341742</t>
+          <t>342198</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>467838</t>
+          <t>469722</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10328,12 +10328,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10348,12 +10348,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>574196</t>
+          <t>575422</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>733552</t>
+          <t>738708</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10363,12 +10363,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>39922</t>
+          <t>41223</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>70744</t>
+          <t>72335</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>80705</t>
+          <t>83038</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>123893</t>
+          <t>124844</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>130056</t>
+          <t>133238</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>186467</t>
+          <t>186084</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10476,12 +10476,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -10504,12 +10504,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16823</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10524,44 +10524,44 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>10386</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>6128</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>17781</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>10386</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>6093</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>17202</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>28</t>
@@ -10574,12 +10574,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13557</t>
+          <t>13453</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>29499</t>
+          <t>30647</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36A-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106481</t>
+          <t>106162</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>148171</t>
+          <t>149495</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80866</t>
+          <t>81453</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>119674</t>
+          <t>122314</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>195746</t>
+          <t>196470</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>256120</t>
+          <t>256795</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>161963</t>
+          <t>161382</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>215717</t>
+          <t>215986</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>203530</t>
+          <t>201435</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259583</t>
+          <t>259709</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>378371</t>
+          <t>377852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>454926</t>
+          <t>459615</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>266772</t>
+          <t>264528</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>327848</t>
+          <t>323323</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>409589</t>
+          <t>411408</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>480601</t>
+          <t>480017</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>697011</t>
+          <t>690411</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>788285</t>
+          <t>787691</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,47%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>239589</t>
+          <t>242663</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>298463</t>
+          <t>298016</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>395533</t>
+          <t>395594</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>464911</t>
+          <t>466467</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>649260</t>
+          <t>653494</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>739807</t>
+          <t>740596</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67181</t>
+          <t>66142</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>103458</t>
+          <t>103580</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102633</t>
+          <t>104499</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>147151</t>
+          <t>147993</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>180218</t>
+          <t>181708</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>235013</t>
+          <t>237993</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>297839</t>
+          <t>295497</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>366224</t>
+          <t>363974</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>183654</t>
+          <t>184927</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>240063</t>
+          <t>240697</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>501197</t>
+          <t>494898</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>588007</t>
+          <t>584321</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>499371</t>
+          <t>498863</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>576765</t>
+          <t>579527</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>403564</t>
+          <t>403589</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>480696</t>
+          <t>475545</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>917801</t>
+          <t>925541</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1029521</t>
+          <t>1032123</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,15%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>615966</t>
+          <t>612025</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>701712</t>
+          <t>698329</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>491228</t>
+          <t>492500</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>569528</t>
+          <t>572460</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1130237</t>
+          <t>1123564</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1237879</t>
+          <t>1248797</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>306784</t>
+          <t>305900</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>371119</t>
+          <t>374905</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>378948</t>
+          <t>377615</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>449797</t>
+          <t>451346</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>705342</t>
+          <t>704240</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>805976</t>
+          <t>807227</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60201</t>
+          <t>61837</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>96714</t>
+          <t>97635</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>114686</t>
+          <t>115678</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>160637</t>
+          <t>163452</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>182945</t>
+          <t>186481</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>243579</t>
+          <t>247011</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>62774</t>
+          <t>63073</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>99663</t>
+          <t>101087</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>48222</t>
+          <t>47507</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>76736</t>
+          <t>77508</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>121407</t>
+          <t>119887</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>169588</t>
+          <t>167284</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>119261</t>
+          <t>119563</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>160382</t>
+          <t>161923</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>104525</t>
+          <t>104095</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>145879</t>
+          <t>144478</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>232118</t>
+          <t>231276</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>290855</t>
+          <t>288799</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,07%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>137661</t>
+          <t>137126</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>180687</t>
+          <t>184233</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>125699</t>
+          <t>124019</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>167711</t>
+          <t>165791</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>275379</t>
+          <t>276997</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>333303</t>
+          <t>340001</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,58%</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>63384</t>
+          <t>63237</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>100035</t>
+          <t>100732</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>75036</t>
+          <t>77371</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>113506</t>
+          <t>113083</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>148383</t>
+          <t>149879</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>199558</t>
+          <t>199440</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,46%</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9292</t>
+          <t>9026</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25855</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20755</t>
+          <t>20690</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43642</t>
+          <t>42399</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33750</t>
+          <t>34057</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61422</t>
+          <t>63047</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>490205</t>
+          <t>493735</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>580476</t>
+          <t>580735</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>337337</t>
+          <t>333440</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>410985</t>
+          <t>411349</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>849138</t>
+          <t>852709</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>967855</t>
+          <t>972306</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>813749</t>
+          <t>814975</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>919064</t>
+          <t>917930</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>741876</t>
+          <t>740176</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>844043</t>
+          <t>845374</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1582711</t>
+          <t>1587948</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1733062</t>
+          <t>1730363</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1058368</t>
+          <t>1055462</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1162001</t>
+          <t>1165299</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1064748</t>
+          <t>1059012</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1174349</t>
+          <t>1173649</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2141634</t>
+          <t>2152032</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2299710</t>
+          <t>2307559</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,54%</t>
         </is>
       </c>
     </row>
@@ -3456,12 +3456,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>642860</t>
+          <t>639083</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>734932</t>
+          <t>736751</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>883378</t>
+          <t>880271</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>991620</t>
+          <t>991740</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1553576</t>
+          <t>1548931</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1695728</t>
+          <t>1694359</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>153493</t>
+          <t>151175</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>204458</t>
+          <t>202945</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>260517</t>
+          <t>258177</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>329993</t>
+          <t>324691</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>428052</t>
+          <t>426300</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>512507</t>
+          <t>513626</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91310</t>
+          <t>90580</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>129954</t>
+          <t>129874</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74998</t>
+          <t>74634</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111707</t>
+          <t>114530</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>176010</t>
+          <t>177842</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>230314</t>
+          <t>230919</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -4256,12 +4256,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>145435</t>
+          <t>145221</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>191662</t>
+          <t>190806</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>204080</t>
+          <t>201595</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>258866</t>
+          <t>256660</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>364557</t>
+          <t>363854</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>436132</t>
+          <t>435942</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -4369,12 +4369,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>201970</t>
+          <t>202258</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>251538</t>
+          <t>250545</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>304809</t>
+          <t>302411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>364016</t>
+          <t>362359</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>520981</t>
+          <t>521908</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>595978</t>
+          <t>599477</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,98%</t>
         </is>
       </c>
     </row>
@@ -4482,12 +4482,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>151417</t>
+          <t>152829</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>198202</t>
+          <t>197232</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4497,12 +4497,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>223800</t>
+          <t>223696</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>280864</t>
+          <t>282286</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4532,12 +4532,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>394869</t>
+          <t>389912</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>467851</t>
+          <t>462379</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4567,12 +4567,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -4595,12 +4595,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45335</t>
+          <t>45883</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73533</t>
+          <t>73015</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4610,12 +4610,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55105</t>
+          <t>54458</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89056</t>
+          <t>88724</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>107745</t>
+          <t>108002</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>151773</t>
+          <t>150263</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308749</t>
+          <t>307878</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>380179</t>
+          <t>383301</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>217963</t>
+          <t>217773</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>276884</t>
+          <t>281318</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>545614</t>
+          <t>548968</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>636224</t>
+          <t>634299</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>527681</t>
+          <t>526144</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>608800</t>
+          <t>611190</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>514616</t>
+          <t>510547</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>595578</t>
+          <t>590425</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1064877</t>
+          <t>1055982</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1179216</t>
+          <t>1175508</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -5164,12 +5164,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>699094</t>
+          <t>696010</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>784974</t>
+          <t>788916</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>690279</t>
+          <t>689799</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>775165</t>
+          <t>778824</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5214,12 +5214,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1409514</t>
+          <t>1404154</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1533529</t>
+          <t>1535332</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,55%</t>
         </is>
       </c>
     </row>
@@ -5277,12 +5277,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>281622</t>
+          <t>275082</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>347360</t>
+          <t>345776</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5292,12 +5292,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>300226</t>
+          <t>303795</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>367878</t>
+          <t>371453</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>596106</t>
+          <t>598781</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>692415</t>
+          <t>693628</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -5390,12 +5390,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>50196</t>
+          <t>49113</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>80503</t>
+          <t>80186</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5405,12 +5405,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70733</t>
+          <t>73033</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>110790</t>
+          <t>111956</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>130109</t>
+          <t>129632</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>180562</t>
+          <t>183095</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -5733,12 +5733,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>89712</t>
+          <t>88449</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>129258</t>
+          <t>126906</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5748,12 +5748,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>64321</t>
+          <t>65185</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>99200</t>
+          <t>99668</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>165104</t>
+          <t>164718</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>214203</t>
+          <t>214143</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -5846,12 +5846,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>153649</t>
+          <t>152980</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>201423</t>
+          <t>197515</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>157880</t>
+          <t>153451</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>198994</t>
+          <t>199290</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>322818</t>
+          <t>320653</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>383649</t>
+          <t>384292</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,5%</t>
         </is>
       </c>
     </row>
@@ -5959,12 +5959,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>151400</t>
+          <t>150987</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>197963</t>
+          <t>194714</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5974,12 +5974,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5994,12 +5994,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>162292</t>
+          <t>160262</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>206884</t>
+          <t>206031</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6009,12 +6009,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>322717</t>
+          <t>325682</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>385482</t>
+          <t>386618</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -6072,12 +6072,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>59797</t>
+          <t>59886</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>93143</t>
+          <t>93867</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69978</t>
+          <t>70223</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>105129</t>
+          <t>107127</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6142,12 +6142,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>138462</t>
+          <t>137186</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>190587</t>
+          <t>189013</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -6185,12 +6185,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18195</t>
+          <t>17835</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6220,12 +6220,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7606</t>
+          <t>7863</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21782</t>
+          <t>23036</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16474</t>
+          <t>15606</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35538</t>
+          <t>36067</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -6528,12 +6528,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>521092</t>
+          <t>517355</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>603113</t>
+          <t>607063</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>380884</t>
+          <t>382340</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>459284</t>
+          <t>454355</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6598,12 +6598,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>923295</t>
+          <t>920033</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1042759</t>
+          <t>1041000</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -6641,12 +6641,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>862086</t>
+          <t>857149</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>964137</t>
+          <t>968755</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6676,12 +6676,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>910218</t>
+          <t>910955</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1014763</t>
+          <t>1018422</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6711,12 +6711,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1800936</t>
+          <t>1802882</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1953823</t>
+          <t>1944397</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -6754,12 +6754,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1082264</t>
+          <t>1083247</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1193634</t>
+          <t>1195864</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6789,12 +6789,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1188543</t>
+          <t>1196221</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1297369</t>
+          <t>1306072</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6824,12 +6824,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2300888</t>
+          <t>2303064</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2467879</t>
+          <t>2465443</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>520530</t>
+          <t>522615</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>608254</t>
+          <t>610985</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6882,12 +6882,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>627604</t>
+          <t>623264</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>719064</t>
+          <t>719720</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1172141</t>
+          <t>1166725</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1306750</t>
+          <t>1298275</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -6980,12 +6980,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>109060</t>
+          <t>110541</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>155533</t>
+          <t>156433</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6995,12 +6995,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>148251</t>
+          <t>148766</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>202345</t>
+          <t>202636</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>272383</t>
+          <t>274776</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>344650</t>
+          <t>343272</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -7549,32 +7549,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>116956</t>
+          <t>142199</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99001</t>
+          <t>121747</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>134808</t>
+          <t>164843</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7584,32 +7584,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>119340</t>
+          <t>134112</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>105737</t>
+          <t>118028</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134161</t>
+          <t>151959</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7619,32 +7619,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>236296</t>
+          <t>276311</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>214440</t>
+          <t>250815</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>260278</t>
+          <t>305356</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -7662,32 +7662,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>152156</t>
+          <t>167793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>134091</t>
+          <t>146194</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>172452</t>
+          <t>188226</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7697,32 +7697,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>252275</t>
+          <t>277097</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>233322</t>
+          <t>256655</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>272627</t>
+          <t>297481</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7732,32 +7732,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>404432</t>
+          <t>444890</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>380225</t>
+          <t>417115</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>431746</t>
+          <t>473624</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,33%</t>
         </is>
       </c>
     </row>
@@ -7775,32 +7775,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>150624</t>
+          <t>165768</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>132770</t>
+          <t>145783</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>168873</t>
+          <t>187449</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7810,32 +7810,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>232196</t>
+          <t>253768</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>215434</t>
+          <t>233247</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>254928</t>
+          <t>275369</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7845,32 +7845,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>382820</t>
+          <t>419536</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>355535</t>
+          <t>393873</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>407779</t>
+          <t>448162</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,48%</t>
         </is>
       </c>
     </row>
@@ -7888,32 +7888,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67707</t>
+          <t>74154</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52674</t>
+          <t>59397</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80854</t>
+          <t>90173</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7923,32 +7923,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>108462</t>
+          <t>108470</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92536</t>
+          <t>93629</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>128206</t>
+          <t>122930</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7958,32 +7958,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>176169</t>
+          <t>182624</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>156357</t>
+          <t>163113</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>201649</t>
+          <t>205198</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -8001,69 +8001,69 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>17472</t>
+          <t>17796</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10855</t>
+          <t>11621</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25401</t>
+          <t>26459</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>31117</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>23395</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>40450</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
           <t>5,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>27184</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>20141</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>35390</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>75</t>
@@ -8071,22 +8071,22 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>44656</t>
+          <t>48913</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34531</t>
+          <t>38087</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>57483</t>
+          <t>60969</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -8114,32 +8114,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>838</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8149,32 +8149,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8635</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8184,27 +8184,27 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>6522</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12838</t>
+          <t>14270</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -8227,17 +8227,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>507779</t>
+          <t>570809</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>507779</t>
+          <t>570809</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>507779</t>
+          <t>570809</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8262,17 +8262,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>743116</t>
+          <t>808882</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>743116</t>
+          <t>808882</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>743116</t>
+          <t>808882</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8297,17 +8297,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1250895</t>
+          <t>1379691</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1250895</t>
+          <t>1379691</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1250895</t>
+          <t>1379691</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8344,32 +8344,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>860272</t>
+          <t>690440</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>670719</t>
+          <t>636302</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1309984</t>
+          <t>744419</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8379,32 +8379,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>418098</t>
+          <t>473702</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>293575</t>
+          <t>440103</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>477479</t>
+          <t>510292</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8414,32 +8414,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1278370</t>
+          <t>1164142</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1044332</t>
+          <t>1103212</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1835947</t>
+          <t>1232178</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -8457,32 +8457,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>748326</t>
+          <t>794065</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536973</t>
+          <t>741886</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>860913</t>
+          <t>844981</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8492,32 +8492,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>720313</t>
+          <t>774852</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>534975</t>
+          <t>734231</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>827023</t>
+          <t>817084</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8527,32 +8527,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1468639</t>
+          <t>1568917</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1163555</t>
+          <t>1501601</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1637271</t>
+          <t>1638890</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>37,36%</t>
         </is>
       </c>
     </row>
@@ -8570,32 +8570,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>502915</t>
+          <t>555514</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>356477</t>
+          <t>510076</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>580682</t>
+          <t>604334</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8605,32 +8605,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>793472</t>
+          <t>578660</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>605852</t>
+          <t>540676</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1208543</t>
+          <t>620110</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8640,32 +8640,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1296387</t>
+          <t>1134175</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1059273</t>
+          <t>1069918</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1760869</t>
+          <t>1192401</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -8683,32 +8683,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>139259</t>
+          <t>148094</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97484</t>
+          <t>125101</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>173588</t>
+          <t>175814</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8718,32 +8718,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>234967</t>
+          <t>261654</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>169637</t>
+          <t>235454</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>277407</t>
+          <t>296077</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8753,32 +8753,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>374226</t>
+          <t>409748</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>299097</t>
+          <t>372953</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>431869</t>
+          <t>452781</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -8796,32 +8796,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30493</t>
+          <t>33014</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19222</t>
+          <t>22714</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43527</t>
+          <t>47276</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8831,67 +8831,67 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>58734</t>
+          <t>67945</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42038</t>
+          <t>54285</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>76870</t>
+          <t>86746</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>100959</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>82976</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>123005</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
           <t>1,89%</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>89227</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>67981</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>110659</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -8909,32 +8909,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9667</t>
+          <t>9955</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8944,32 +8944,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1774</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8994</t>
+          <t>9599</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8979,32 +8979,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8145</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>15977</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -9022,17 +9022,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2285381</t>
+          <t>2225372</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2285381</t>
+          <t>2225372</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2285381</t>
+          <t>2225372</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9057,17 +9057,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2229612</t>
+          <t>2161568</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2229612</t>
+          <t>2161568</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2229612</t>
+          <t>2161568</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4514994</t>
+          <t>4386940</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4514994</t>
+          <t>4386940</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4514994</t>
+          <t>4386940</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9139,32 +9139,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>191788</t>
+          <t>223509</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>167065</t>
+          <t>195151</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>220410</t>
+          <t>250987</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9174,32 +9174,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>162218</t>
+          <t>178539</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>143479</t>
+          <t>157339</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>200182</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9209,32 +9209,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>354006</t>
+          <t>402047</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>323409</t>
+          <t>366300</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>388181</t>
+          <t>437559</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -9252,32 +9252,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>241992</t>
+          <t>265449</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>216179</t>
+          <t>241131</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>268646</t>
+          <t>293678</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9287,32 +9287,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>228144</t>
+          <t>251449</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>206129</t>
+          <t>230159</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>248507</t>
+          <t>278620</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9322,32 +9322,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>470136</t>
+          <t>516898</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>432362</t>
+          <t>480883</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>502220</t>
+          <t>551816</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,19%</t>
         </is>
       </c>
     </row>
@@ -9365,32 +9365,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>157776</t>
+          <t>162558</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>134111</t>
+          <t>139148</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>185744</t>
+          <t>186027</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9400,32 +9400,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>172722</t>
+          <t>196670</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>153959</t>
+          <t>174071</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>191560</t>
+          <t>217887</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9435,32 +9435,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>330497</t>
+          <t>359228</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>301195</t>
+          <t>328970</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>366376</t>
+          <t>392071</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -9478,22 +9478,22 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>43141</t>
+          <t>47897</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31960</t>
+          <t>35221</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>58196</t>
+          <t>63610</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9513,32 +9513,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>77340</t>
+          <t>86546</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>63989</t>
+          <t>71728</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>94186</t>
+          <t>103450</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9548,32 +9548,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>120481</t>
+          <t>134443</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>101637</t>
+          <t>115578</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>141154</t>
+          <t>160213</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -9591,32 +9591,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>7679</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13719</t>
+          <t>14051</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9626,32 +9626,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>17341</t>
+          <t>18904</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11557</t>
+          <t>12777</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27734</t>
+          <t>30293</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9661,32 +9661,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>24818</t>
+          <t>26584</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17612</t>
+          <t>18602</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38236</t>
+          <t>37920</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -9704,32 +9704,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>861</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8012</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9739,32 +9739,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>760</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>6679</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9774,32 +9774,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>2262</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11054</t>
+          <t>10693</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -9817,17 +9817,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>644906</t>
+          <t>709871</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>644906</t>
+          <t>709871</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>644906</t>
+          <t>709871</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9852,17 +9852,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9887,17 +9887,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1305369</t>
+          <t>1444748</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1305369</t>
+          <t>1444748</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1305369</t>
+          <t>1444748</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9934,32 +9934,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1169016</t>
+          <t>1056148</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>970730</t>
+          <t>998664</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1687344</t>
+          <t>1125897</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9969,32 +9969,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>699656</t>
+          <t>786353</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>560816</t>
+          <t>741129</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>768476</t>
+          <t>831769</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10004,32 +10004,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1868672</t>
+          <t>1842500</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1621534</t>
+          <t>1768482</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2494280</t>
+          <t>1923664</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>26,68%</t>
         </is>
       </c>
     </row>
@@ -10047,32 +10047,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1142474</t>
+          <t>1227306</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>882892</t>
+          <t>1162726</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1259078</t>
+          <t>1285019</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10082,32 +10082,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1200733</t>
+          <t>1303398</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>968947</t>
+          <t>1254091</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1304660</t>
+          <t>1356335</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10117,32 +10117,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2343207</t>
+          <t>2530705</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2032622</t>
+          <t>2446958</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2527688</t>
+          <t>2603203</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>36,1%</t>
         </is>
       </c>
     </row>
@@ -10160,32 +10160,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>811315</t>
+          <t>883840</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>632231</t>
+          <t>828255</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>895763</t>
+          <t>939083</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10195,32 +10195,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1198390</t>
+          <t>1029099</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1015910</t>
+          <t>980532</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1696302</t>
+          <t>1077327</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10230,32 +10230,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2009704</t>
+          <t>1912938</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1780041</t>
+          <t>1843568</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2516337</t>
+          <t>1991247</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>27,61%</t>
         </is>
       </c>
     </row>
@@ -10273,32 +10273,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>250107</t>
+          <t>270145</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>197872</t>
+          <t>236290</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>288719</t>
+          <t>304487</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10308,32 +10308,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>420769</t>
+          <t>456670</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>342198</t>
+          <t>423062</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>469722</t>
+          <t>496578</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10343,32 +10343,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>670876</t>
+          <t>726815</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>575422</t>
+          <t>681914</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>738708</t>
+          <t>773415</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -10386,32 +10386,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>55442</t>
+          <t>58490</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>41223</t>
+          <t>44455</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>72335</t>
+          <t>74591</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>103259</t>
+          <t>117966</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>83038</t>
+          <t>99836</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>124844</t>
+          <t>139094</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10456,32 +10456,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>158700</t>
+          <t>176456</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>133238</t>
+          <t>153847</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>186084</t>
+          <t>202655</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -10499,32 +10499,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>10123</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>18551</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>10386</t>
+          <t>11842</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6128</t>
+          <t>7057</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17781</t>
+          <t>18838</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10569,22 +10569,22 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>21965</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13453</t>
+          <t>13813</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>30647</t>
+          <t>31494</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -10612,17 +10612,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3438066</t>
+          <t>3506051</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3438066</t>
+          <t>3506051</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3438066</t>
+          <t>3506051</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3633192</t>
+          <t>3705328</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3633192</t>
+          <t>3705328</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3633192</t>
+          <t>3705328</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10682,17 +10682,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>7071257</t>
+          <t>7211379</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7071257</t>
+          <t>7211379</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7071257</t>
+          <t>7211379</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
